--- a/MDC/MDC_Precio_t_1.xlsx
+++ b/MDC/MDC_Precio_t_1.xlsx
@@ -1297,7 +1297,7 @@
     <t>06410211.01</t>
   </si>
   <si>
-    <t>Yip's</t>
+    <t>Supermercado 1</t>
   </si>
   <si>
     <t>Precio</t>
@@ -1708,7 +1708,7 @@
     <t>195</t>
   </si>
   <si>
-    <t>La Colonia # 1</t>
+    <t>Supermercado 2</t>
   </si>
   <si>
     <t>59.8</t>
@@ -2116,7 +2116,7 @@
     <t>Foodmart</t>
   </si>
   <si>
-    <t>Los almendros</t>
+    <t>Mercadito 1</t>
   </si>
   <si>
     <t>Mercadito Precio t-1</t>
@@ -2143,7 +2143,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>5 estrellas</t>
+    <t>Mercadito 2</t>
   </si>
   <si>
     <t>31.5</t>
